--- a/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>83443.996</v>
+        <v>83303.717</v>
       </c>
       <c r="C2">
-        <v>77953.973</v>
+        <v>77864.60000000001</v>
       </c>
       <c r="D2">
-        <v>89151.955</v>
+        <v>88960.97500000001</v>
       </c>
       <c r="E2">
-        <v>866602.714</v>
+        <v>866253.572</v>
       </c>
       <c r="F2">
-        <v>833544.023</v>
+        <v>833473.304</v>
       </c>
       <c r="G2">
-        <v>900403.6640000001</v>
+        <v>899737.6869999999</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>55016.203</v>
+        <v>55018.036</v>
       </c>
       <c r="C3">
-        <v>52126.83900000001</v>
+        <v>52064.811</v>
       </c>
       <c r="D3">
-        <v>58012.77699999999</v>
+        <v>58039.923</v>
       </c>
       <c r="E3">
-        <v>49250.982</v>
+        <v>49273.92</v>
       </c>
       <c r="F3">
-        <v>46905.059</v>
+        <v>46932.702</v>
       </c>
       <c r="G3">
-        <v>51733.031</v>
+        <v>51671.494</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>40798.179</v>
+        <v>41026.507</v>
       </c>
       <c r="C4">
-        <v>38654.791</v>
+        <v>38942.642</v>
       </c>
       <c r="D4">
-        <v>43005.231</v>
+        <v>43208.725</v>
       </c>
       <c r="E4">
-        <v>61582.521</v>
+        <v>62126.264</v>
       </c>
       <c r="F4">
-        <v>57697.05</v>
+        <v>58183.771</v>
       </c>
       <c r="G4">
-        <v>65904.77</v>
+        <v>66316.33</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>8329.457999999999</v>
+        <v>8339.161</v>
       </c>
       <c r="C5">
-        <v>7860.565000000001</v>
+        <v>7889.333</v>
       </c>
       <c r="D5">
-        <v>8798.648999999999</v>
+        <v>8804.784</v>
       </c>
       <c r="E5">
-        <v>16291.372</v>
+        <v>16293.296</v>
       </c>
       <c r="F5">
-        <v>15333.761</v>
+        <v>15375.148</v>
       </c>
       <c r="G5">
-        <v>17208.241</v>
+        <v>17241.689</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>19092.818</v>
+        <v>19065.449</v>
       </c>
       <c r="C6">
-        <v>17690.901</v>
+        <v>17630.145</v>
       </c>
       <c r="D6">
-        <v>20627.273</v>
+        <v>20546.139</v>
       </c>
       <c r="E6">
-        <v>31816.418</v>
+        <v>31803.519</v>
       </c>
       <c r="F6">
-        <v>29859.725</v>
+        <v>29904.307</v>
       </c>
       <c r="G6">
-        <v>33742.425</v>
+        <v>33768.322</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>200175.353</v>
+        <v>165965.192</v>
       </c>
       <c r="C7">
-        <v>191754.007</v>
+        <v>158922.827</v>
       </c>
       <c r="D7">
-        <v>208383.427</v>
+        <v>173198.916</v>
       </c>
       <c r="E7">
-        <v>585595.3419999999</v>
+        <v>53957.603</v>
       </c>
       <c r="F7">
-        <v>550632.873</v>
+        <v>50774.781</v>
       </c>
       <c r="G7">
-        <v>620233.216</v>
+        <v>57286.313</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>323412.011</v>
+        <v>289414.345</v>
       </c>
       <c r="C8">
-        <v>308087.103</v>
+        <v>275449.758</v>
       </c>
       <c r="D8">
-        <v>338827.357</v>
+        <v>303798.487</v>
       </c>
       <c r="E8">
-        <v>744536.635</v>
+        <v>213454.602</v>
       </c>
       <c r="F8">
-        <v>700428.4680000001</v>
+        <v>201170.709</v>
       </c>
       <c r="G8">
-        <v>788821.683</v>
+        <v>226284.148</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>406856.007</v>
+        <v>372718.062</v>
       </c>
       <c r="C9">
-        <v>386041.076</v>
+        <v>353314.358</v>
       </c>
       <c r="D9">
-        <v>427979.312</v>
+        <v>392759.462</v>
       </c>
       <c r="E9">
-        <v>1611139.349</v>
+        <v>1079708.174</v>
       </c>
       <c r="F9">
-        <v>1533972.491</v>
+        <v>1034644.013</v>
       </c>
       <c r="G9">
-        <v>1689225.347</v>
+        <v>1126021.835</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
-        <v>83303.717</v>
+        <v>11764.02499999999</v>
       </c>
       <c r="C2">
-        <v>77864.60000000001</v>
+        <v>11226.976</v>
       </c>
       <c r="D2">
-        <v>88960.97500000001</v>
+        <v>12353.519</v>
       </c>
       <c r="E2">
-        <v>866253.572</v>
+        <v>116812.696</v>
       </c>
       <c r="F2">
-        <v>833473.304</v>
+        <v>114631.931</v>
       </c>
       <c r="G2">
-        <v>899737.6869999999</v>
+        <v>119149.172</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
-        <v>55018.036</v>
+        <v>9837.009999999995</v>
       </c>
       <c r="C3">
-        <v>52064.811</v>
+        <v>9514.599000000002</v>
       </c>
       <c r="D3">
-        <v>58039.923</v>
+        <v>10165.268</v>
       </c>
       <c r="E3">
-        <v>49273.92</v>
+        <v>8574.506000000001</v>
       </c>
       <c r="F3">
-        <v>46932.702</v>
+        <v>8345.201999999997</v>
       </c>
       <c r="G3">
-        <v>51671.494</v>
+        <v>8799.951000000001</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
-        <v>41026.507</v>
+        <v>8637.283000000003</v>
       </c>
       <c r="C4">
-        <v>38942.642</v>
+        <v>8384.126999999997</v>
       </c>
       <c r="D4">
-        <v>43208.725</v>
+        <v>8906.983</v>
       </c>
       <c r="E4">
-        <v>62126.264</v>
+        <v>13058.022</v>
       </c>
       <c r="F4">
-        <v>58183.771</v>
+        <v>12515.109</v>
       </c>
       <c r="G4">
-        <v>66316.33</v>
+        <v>13613.314</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
-        <v>8339.161</v>
+        <v>1743.229</v>
       </c>
       <c r="C5">
-        <v>7889.333</v>
+        <v>1687.721</v>
       </c>
       <c r="D5">
-        <v>8804.784</v>
+        <v>1796.803000000001</v>
       </c>
       <c r="E5">
-        <v>16293.296</v>
+        <v>3401.083999999999</v>
       </c>
       <c r="F5">
-        <v>15375.148</v>
+        <v>3284.037999999999</v>
       </c>
       <c r="G5">
-        <v>17241.689</v>
+        <v>3518.219000000001</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
-        <v>19065.449</v>
+        <v>3459.254000000001</v>
       </c>
       <c r="C6">
-        <v>17630.145</v>
+        <v>3282.745999999999</v>
       </c>
       <c r="D6">
-        <v>20546.139</v>
+        <v>3647.252000000002</v>
       </c>
       <c r="E6">
-        <v>31803.519</v>
+        <v>5520.523000000001</v>
       </c>
       <c r="F6">
-        <v>29904.307</v>
+        <v>5332.148000000001</v>
       </c>
       <c r="G6">
-        <v>33768.322</v>
+        <v>5715.957000000002</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
-        <v>165965.192</v>
+        <v>33349.50300000001</v>
       </c>
       <c r="C7">
-        <v>158922.827</v>
+        <v>32534.48000000001</v>
       </c>
       <c r="D7">
-        <v>173198.916</v>
+        <v>34180.93100000001</v>
       </c>
       <c r="E7">
-        <v>53957.603</v>
+        <v>10644.381</v>
       </c>
       <c r="F7">
-        <v>50774.781</v>
+        <v>10288.785</v>
       </c>
       <c r="G7">
-        <v>57286.313</v>
+        <v>11000.962</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
-        <v>289414.345</v>
+        <v>57026.27900000001</v>
       </c>
       <c r="C8">
-        <v>275449.758</v>
+        <v>55403.67299999998</v>
       </c>
       <c r="D8">
-        <v>303798.487</v>
+        <v>58697.23700000002</v>
       </c>
       <c r="E8">
-        <v>213454.602</v>
+        <v>41198.516</v>
       </c>
       <c r="F8">
-        <v>201170.709</v>
+        <v>39765.28200000001</v>
       </c>
       <c r="G8">
-        <v>226284.148</v>
+        <v>42648.40299999999</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
-        <v>372718.062</v>
+        <v>68790.30399999995</v>
       </c>
       <c r="C9">
-        <v>353314.358</v>
+        <v>66630.64899999998</v>
       </c>
       <c r="D9">
-        <v>392759.462</v>
+        <v>71050.75599999999</v>
       </c>
       <c r="E9">
-        <v>1079708.174</v>
+        <v>158011.2120000001</v>
       </c>
       <c r="F9">
-        <v>1034644.013</v>
+        <v>154397.213</v>
       </c>
       <c r="G9">
-        <v>1126021.835</v>
+        <v>161797.5749999998</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:L9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -390,6 +390,31 @@
           <t>tot_daly_up</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>tot_medic_costs_low</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -415,6 +440,21 @@
       <c r="G2">
         <v>119149.172</v>
       </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>15849534998.181</v>
+      </c>
+      <c r="K2">
+        <v>15536600126.063</v>
+      </c>
+      <c r="L2">
+        <v>15246777407.965</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -440,6 +480,21 @@
       <c r="G3">
         <v>8799.951000000001</v>
       </c>
+      <c r="H3">
+        <v>547859793.7000003</v>
+      </c>
+      <c r="I3">
+        <v>530428010.9750001</v>
+      </c>
+      <c r="J3">
+        <v>1170416768.516999</v>
+      </c>
+      <c r="K3">
+        <v>1139888078.452</v>
+      </c>
+      <c r="L3">
+        <v>1110942512.516</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -465,6 +520,21 @@
       <c r="G4">
         <v>13613.314</v>
       </c>
+      <c r="H4">
+        <v>127920587.883</v>
+      </c>
+      <c r="I4">
+        <v>124051264.853</v>
+      </c>
+      <c r="J4">
+        <v>1810067213.433001</v>
+      </c>
+      <c r="K4">
+        <v>1736176681.174</v>
+      </c>
+      <c r="L4">
+        <v>1670253278.349</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -490,6 +560,21 @@
       <c r="G5">
         <v>3518.219000000001</v>
       </c>
+      <c r="H5">
+        <v>131017505.138</v>
+      </c>
+      <c r="I5">
+        <v>126982695.595</v>
+      </c>
+      <c r="J5">
+        <v>468293886.3610001</v>
+      </c>
+      <c r="K5">
+        <v>452012968.6139998</v>
+      </c>
+      <c r="L5">
+        <v>436662147.8710001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -515,6 +600,21 @@
       <c r="G6">
         <v>5715.957000000002</v>
       </c>
+      <c r="H6">
+        <v>58237615.69700003</v>
+      </c>
+      <c r="I6">
+        <v>55248297.49200001</v>
+      </c>
+      <c r="J6">
+        <v>760624801.395</v>
+      </c>
+      <c r="K6">
+        <v>733643839.7470002</v>
+      </c>
+      <c r="L6">
+        <v>708958391.7550001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -540,6 +640,21 @@
       <c r="G7">
         <v>11000.962</v>
       </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1463919239.634</v>
+      </c>
+      <c r="K7">
+        <v>1416012130.155999</v>
+      </c>
+      <c r="L7">
+        <v>1369206636.319</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -565,6 +680,21 @@
       <c r="G8">
         <v>42648.40299999999</v>
       </c>
+      <c r="H8">
+        <v>865035502.4180012</v>
+      </c>
+      <c r="I8">
+        <v>836710268.915</v>
+      </c>
+      <c r="J8">
+        <v>5673321909.34</v>
+      </c>
+      <c r="K8">
+        <v>5477733698.142998</v>
+      </c>
+      <c r="L8">
+        <v>5296022966.809998</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -573,10 +703,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>68790.30399999995</v>
+        <v>68790.304</v>
       </c>
       <c r="C9">
-        <v>66630.64899999998</v>
+        <v>66630.64900000003</v>
       </c>
       <c r="D9">
         <v>71050.75599999999</v>
@@ -589,6 +719,21 @@
       </c>
       <c r="G9">
         <v>161797.5749999998</v>
+      </c>
+      <c r="H9">
+        <v>865035502.4180012</v>
+      </c>
+      <c r="I9">
+        <v>836710268.915</v>
+      </c>
+      <c r="J9">
+        <v>21522856907.521</v>
+      </c>
+      <c r="K9">
+        <v>21014333824.20601</v>
+      </c>
+      <c r="L9">
+        <v>20542800374.77501</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -402,17 +402,22 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>tot_medic_costs_up</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>tot_soc_costs_low</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
           <t>tot_soc_costs_up</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
         </is>
       </c>
     </row>
@@ -447,7 +452,7 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>15849534998.181</v>
+        <v>0</v>
       </c>
       <c r="K2">
         <v>15536600126.063</v>
@@ -455,6 +460,9 @@
       <c r="L2">
         <v>15246777407.965</v>
       </c>
+      <c r="M2">
+        <v>15849534998.181</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -487,7 +495,7 @@
         <v>530428010.9750001</v>
       </c>
       <c r="J3">
-        <v>1170416768.516999</v>
+        <v>566462290.8530002</v>
       </c>
       <c r="K3">
         <v>1139888078.452</v>
@@ -495,6 +503,9 @@
       <c r="L3">
         <v>1110942512.516</v>
       </c>
+      <c r="M3">
+        <v>1170416768.516999</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -527,7 +538,7 @@
         <v>124051264.853</v>
       </c>
       <c r="J4">
-        <v>1810067213.433001</v>
+        <v>131892757.554</v>
       </c>
       <c r="K4">
         <v>1736176681.174</v>
@@ -535,6 +546,9 @@
       <c r="L4">
         <v>1670253278.349</v>
       </c>
+      <c r="M4">
+        <v>1810067213.433001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -567,7 +581,7 @@
         <v>126982695.595</v>
       </c>
       <c r="J5">
-        <v>468293886.3610001</v>
+        <v>135351726.447</v>
       </c>
       <c r="K5">
         <v>452012968.6139998</v>
@@ -575,6 +589,9 @@
       <c r="L5">
         <v>436662147.8710001</v>
       </c>
+      <c r="M5">
+        <v>468293886.3610001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -607,7 +624,7 @@
         <v>55248297.49200001</v>
       </c>
       <c r="J6">
-        <v>760624801.395</v>
+        <v>61338518.73499998</v>
       </c>
       <c r="K6">
         <v>733643839.7470002</v>
@@ -615,6 +632,9 @@
       <c r="L6">
         <v>708958391.7550001</v>
       </c>
+      <c r="M6">
+        <v>760624801.395</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,7 +667,7 @@
         <v>0</v>
       </c>
       <c r="J7">
-        <v>1463919239.634</v>
+        <v>0</v>
       </c>
       <c r="K7">
         <v>1416012130.155999</v>
@@ -655,6 +675,9 @@
       <c r="L7">
         <v>1369206636.319</v>
       </c>
+      <c r="M7">
+        <v>1463919239.634</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -687,7 +710,7 @@
         <v>836710268.915</v>
       </c>
       <c r="J8">
-        <v>5673321909.34</v>
+        <v>895045293.5889997</v>
       </c>
       <c r="K8">
         <v>5477733698.142998</v>
@@ -695,6 +718,9 @@
       <c r="L8">
         <v>5296022966.809998</v>
       </c>
+      <c r="M8">
+        <v>5673321909.34</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -727,13 +753,16 @@
         <v>836710268.915</v>
       </c>
       <c r="J9">
-        <v>21522856907.521</v>
+        <v>895045293.5889997</v>
       </c>
       <c r="K9">
         <v>21014333824.20601</v>
       </c>
       <c r="L9">
         <v>20542800374.77501</v>
+      </c>
+      <c r="M9">
+        <v>21522856907.521</v>
       </c>
     </row>
   </sheetData>

--- a/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
+++ b/output/Tables/Modal shift/HIA_modal_shift_added_1000replicate.xlsx
@@ -1,21 +1,108 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10119"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ines/Documents/PhD/PROJETS/MARCHE/HIA_walking_steps/output/Tables/Modal shift/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{853AEB87-2AD3-4841-8B1A-6FE6554CE8D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="16100" windowHeight="9660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+  <si>
+    <t>disease</t>
+  </si>
+  <si>
+    <t>tot_cases</t>
+  </si>
+  <si>
+    <t>tot_cases_low</t>
+  </si>
+  <si>
+    <t>tot_cases_up</t>
+  </si>
+  <si>
+    <t>tot_daly</t>
+  </si>
+  <si>
+    <t>tot_daly_low</t>
+  </si>
+  <si>
+    <t>tot_daly_up</t>
+  </si>
+  <si>
+    <t>tot_medic_costs</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_low</t>
+  </si>
+  <si>
+    <t>tot_medic_costs_up</t>
+  </si>
+  <si>
+    <t>tot_soc_costs</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_low</t>
+  </si>
+  <si>
+    <t>tot_soc_costs_up</t>
+  </si>
+  <si>
+    <t>mort</t>
+  </si>
+  <si>
+    <t>cvd</t>
+  </si>
+  <si>
+    <t>cancer</t>
+  </si>
+  <si>
+    <t>diab2</t>
+  </si>
+  <si>
+    <t>dem</t>
+  </si>
+  <si>
+    <t>dep</t>
+  </si>
+  <si>
+    <t>Morbidity</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -63,13 +150,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -107,7 +202,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -141,6 +236,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -175,9 +271,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -350,88 +447,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="10.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="7" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>disease</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_low</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>tot_cases_up</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_low</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>tot_daly_up</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_low</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>tot_medic_costs_up</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_low</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>tot_soc_costs_up</t>
-        </is>
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>mort</t>
-        </is>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>13</v>
       </c>
       <c r="B2">
-        <v>11764.02499999999</v>
+        <v>11764.024999999991</v>
       </c>
       <c r="C2">
-        <v>11226.976</v>
+        <v>11226.976000000001</v>
       </c>
       <c r="D2">
         <v>12353.519</v>
@@ -443,7 +523,7 @@
         <v>114631.931</v>
       </c>
       <c r="G2">
-        <v>119149.172</v>
+        <v>119149.17200000001</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -464,14 +544,12 @@
         <v>15849534998.181</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>cvd</t>
-        </is>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>14</v>
       </c>
       <c r="B3">
-        <v>9837.009999999995</v>
+        <v>9837.0099999999948</v>
       </c>
       <c r="C3">
         <v>9514.599000000002</v>
@@ -480,25 +558,25 @@
         <v>10165.268</v>
       </c>
       <c r="E3">
-        <v>8574.506000000001</v>
+        <v>8574.5060000000012</v>
       </c>
       <c r="F3">
-        <v>8345.201999999997</v>
+        <v>8345.2019999999975</v>
       </c>
       <c r="G3">
-        <v>8799.951000000001</v>
+        <v>8799.9510000000009</v>
       </c>
       <c r="H3">
-        <v>547859793.7000003</v>
+        <v>547859793.70000029</v>
       </c>
       <c r="I3">
-        <v>530428010.9750001</v>
+        <v>530428010.97500008</v>
       </c>
       <c r="J3">
-        <v>566462290.8530002</v>
+        <v>566462290.85300016</v>
       </c>
       <c r="K3">
-        <v>1139888078.452</v>
+        <v>1139888078.4519999</v>
       </c>
       <c r="L3">
         <v>1110942512.516</v>
@@ -507,23 +585,21 @@
         <v>1170416768.516999</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cancer</t>
-        </is>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>15</v>
       </c>
       <c r="B4">
-        <v>8637.283000000003</v>
+        <v>8637.2830000000031</v>
       </c>
       <c r="C4">
-        <v>8384.126999999997</v>
+        <v>8384.1269999999968</v>
       </c>
       <c r="D4">
-        <v>8906.983</v>
+        <v>8906.9830000000002</v>
       </c>
       <c r="E4">
-        <v>13058.022</v>
+        <v>13058.022000000001</v>
       </c>
       <c r="F4">
         <v>12515.109</v>
@@ -538,7 +614,7 @@
         <v>124051264.853</v>
       </c>
       <c r="J4">
-        <v>131892757.554</v>
+        <v>131892757.55400001</v>
       </c>
       <c r="K4">
         <v>1736176681.174</v>
@@ -550,11 +626,9 @@
         <v>1810067213.433001</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>diab2</t>
-        </is>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>16</v>
       </c>
       <c r="B5">
         <v>1743.229</v>
@@ -566,10 +640,10 @@
         <v>1796.803000000001</v>
       </c>
       <c r="E5">
-        <v>3401.083999999999</v>
+        <v>3401.0839999999989</v>
       </c>
       <c r="F5">
-        <v>3284.037999999999</v>
+        <v>3284.0379999999991</v>
       </c>
       <c r="G5">
         <v>3518.219000000001</v>
@@ -584,29 +658,27 @@
         <v>135351726.447</v>
       </c>
       <c r="K5">
-        <v>452012968.6139998</v>
+        <v>452012968.61399978</v>
       </c>
       <c r="L5">
-        <v>436662147.8710001</v>
+        <v>436662147.87100011</v>
       </c>
       <c r="M5">
-        <v>468293886.3610001</v>
+        <v>468293886.36100012</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>dem</t>
-        </is>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>17</v>
       </c>
       <c r="B6">
-        <v>3459.254000000001</v>
+        <v>3459.2540000000008</v>
       </c>
       <c r="C6">
-        <v>3282.745999999999</v>
+        <v>3282.7459999999992</v>
       </c>
       <c r="D6">
-        <v>3647.252000000002</v>
+        <v>3647.2520000000022</v>
       </c>
       <c r="E6">
         <v>5520.523000000001</v>
@@ -615,44 +687,42 @@
         <v>5332.148000000001</v>
       </c>
       <c r="G6">
-        <v>5715.957000000002</v>
+        <v>5715.9570000000022</v>
       </c>
       <c r="H6">
-        <v>58237615.69700003</v>
+        <v>58237615.697000027</v>
       </c>
       <c r="I6">
-        <v>55248297.49200001</v>
+        <v>55248297.492000014</v>
       </c>
       <c r="J6">
-        <v>61338518.73499998</v>
+        <v>61338518.734999977</v>
       </c>
       <c r="K6">
-        <v>733643839.7470002</v>
+        <v>733643839.74700022</v>
       </c>
       <c r="L6">
-        <v>708958391.7550001</v>
+        <v>708958391.75500011</v>
       </c>
       <c r="M6">
-        <v>760624801.395</v>
+        <v>760624801.39499998</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>dep</t>
-        </is>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>18</v>
       </c>
       <c r="B7">
-        <v>33349.50300000001</v>
+        <v>33349.503000000012</v>
       </c>
       <c r="C7">
         <v>32534.48000000001</v>
       </c>
       <c r="D7">
-        <v>34180.93100000001</v>
+        <v>34180.931000000011</v>
       </c>
       <c r="E7">
-        <v>10644.381</v>
+        <v>10644.380999999999</v>
       </c>
       <c r="F7">
         <v>10288.785</v>
@@ -670,96 +740,92 @@
         <v>0</v>
       </c>
       <c r="K7">
-        <v>1416012130.155999</v>
+        <v>1416012130.1559989</v>
       </c>
       <c r="L7">
         <v>1369206636.319</v>
       </c>
       <c r="M7">
-        <v>1463919239.634</v>
+        <v>1463919239.6340001</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Morbidity</t>
-        </is>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>19</v>
       </c>
       <c r="B8">
         <v>57026.27900000001</v>
       </c>
       <c r="C8">
-        <v>55403.67299999998</v>
+        <v>55403.672999999981</v>
       </c>
       <c r="D8">
-        <v>58697.23700000002</v>
+        <v>58697.237000000023</v>
       </c>
       <c r="E8">
-        <v>41198.516</v>
+        <v>41198.516000000003</v>
       </c>
       <c r="F8">
-        <v>39765.28200000001</v>
+        <v>39765.282000000007</v>
       </c>
       <c r="G8">
-        <v>42648.40299999999</v>
+        <v>42648.402999999991</v>
       </c>
       <c r="H8">
-        <v>865035502.4180012</v>
+        <v>865035502.41800117</v>
       </c>
       <c r="I8">
-        <v>836710268.915</v>
+        <v>836710268.91499996</v>
       </c>
       <c r="J8">
-        <v>895045293.5889997</v>
+        <v>895045293.58899975</v>
       </c>
       <c r="K8">
-        <v>5477733698.142998</v>
+        <v>5477733698.1429977</v>
       </c>
       <c r="L8">
-        <v>5296022966.809998</v>
+        <v>5296022966.8099976</v>
       </c>
       <c r="M8">
-        <v>5673321909.34</v>
+        <v>5673321909.3400002</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>68790.304</v>
+        <v>68790.304000000004</v>
       </c>
       <c r="C9">
-        <v>66630.64900000003</v>
+        <v>66630.649000000034</v>
       </c>
       <c r="D9">
-        <v>71050.75599999999</v>
+        <v>71050.755999999994</v>
       </c>
       <c r="E9">
-        <v>158011.2120000001</v>
+        <v>158011.21200000009</v>
       </c>
       <c r="F9">
-        <v>154397.213</v>
+        <v>154397.21299999999</v>
       </c>
       <c r="G9">
-        <v>161797.5749999998</v>
+        <v>161797.57499999981</v>
       </c>
       <c r="H9">
-        <v>865035502.4180012</v>
+        <v>865035502.41800117</v>
       </c>
       <c r="I9">
-        <v>836710268.915</v>
+        <v>836710268.91499996</v>
       </c>
       <c r="J9">
-        <v>895045293.5889997</v>
+        <v>895045293.58899975</v>
       </c>
       <c r="K9">
-        <v>21014333824.20601</v>
+        <v>21014333824.206009</v>
       </c>
       <c r="L9">
-        <v>20542800374.77501</v>
+        <v>20542800374.775009</v>
       </c>
       <c r="M9">
         <v>21522856907.521</v>
